--- a/Sergio i Dome/Informe pràctica H_20250408.xlsx
+++ b/Sergio i Dome/Informe pràctica H_20250408.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uab-my.sharepoint.com/personal/1479474_uab_cat/Documents/TEACHING/UAB/2024-2025/S2_LACE/3__informes/plantilles/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deumenec/Documents/Uni/LACE/Sergio i Dome/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="11_76D4419BBD0DC5B4564594EB90AF1A60D1CE558E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8B3AFCD-3C12-4EDE-B34B-A8D065476FA4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE7F6A7-1E48-7C47-BFFF-7895B9585395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="15120" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pràctica H" sheetId="1" r:id="rId1"/>
@@ -36,8 +36,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
   <si>
     <t>Informe pràctica H</t>
   </si>
@@ -180,6 +202,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>0</t>
     </r>
@@ -203,6 +226,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>0</t>
     </r>
@@ -215,6 +239,42 @@
       </rPr>
       <t xml:space="preserve"> (descafeinat)</t>
     </r>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>area:</t>
+  </si>
+  <si>
+    <t>concentració=</t>
+  </si>
+  <si>
+    <t>ppm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a la mostra hi havia </t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>A la mostra hi ha</t>
+  </si>
+  <si>
+    <t>g caf</t>
+  </si>
+  <si>
+    <t>mg</t>
+  </si>
+  <si>
+    <t>Truecaf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Va caldre repetir el patró 3 perqué en una primera repetició </t>
   </si>
 </sst>
 </file>
@@ -267,6 +327,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -439,13 +500,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -455,9 +510,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -472,7 +524,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -490,6 +551,1281 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Caf</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-3.0888456301594296E-2"/>
+                  <c:y val="-1.5190416613294642E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-ES"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Pràctica H'!$D$24:$D$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.0379999999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.0759999999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.1519999999999992</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.228</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20.38</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Pràctica H'!$E$24:$E$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>208195</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>424659</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>821661</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1205257</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1994397</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1741-F545-AF21-29634575362B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1722708448"/>
+        <c:axId val="1722511248"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1722708448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1722511248"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1722511248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1722708448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>44172</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>53007</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1358347</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>3776868</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD88FB96-EBF4-6F6A-EA2A-7FDC85A6D923}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>817218</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>3794629</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11D942D9-81A3-684A-8010-9F9413D425AE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8404087" y="7432261"/>
+          <a:ext cx="6692348" cy="3794629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1104348</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>565</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{476A8B40-25CB-1E0C-C7F0-FB19E2A31402}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15394609" y="7432261"/>
+          <a:ext cx="6681304" cy="3810565"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>1104348</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>3776389</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5728BF50-2A6B-E966-6240-83EA3CCDF797}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22086957" y="7432261"/>
+          <a:ext cx="6681304" cy="3776389"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>1104348</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>1769</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74428BE5-1C65-2F59-9C2C-2A699F048F17}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28779304" y="7432261"/>
+          <a:ext cx="6681305" cy="3811769"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>3802079</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4998EAE-350E-BD0A-4953-4ABD4C56D6EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="35471652" y="7432261"/>
+          <a:ext cx="6692348" cy="3802079"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>3774073</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35459A79-67A2-CD90-77A9-D058030F3BCF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="42164000" y="7432261"/>
+          <a:ext cx="6692348" cy="3774073"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>1093305</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>3806723</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA7CCE7D-578A-DC08-560E-708849AF65F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="48856348" y="7432262"/>
+          <a:ext cx="6670261" cy="3806722"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -791,23 +2127,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AW58"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
     <col min="2" max="3" width="14.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.6640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="18" style="1" customWidth="1"/>
-    <col min="7" max="49" width="14.6640625" style="1" customWidth="1"/>
-    <col min="50" max="16384" width="11.44140625" style="1"/>
+    <col min="7" max="10" width="14.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.83203125" style="1" customWidth="1"/>
+    <col min="13" max="49" width="14.6640625" style="1" customWidth="1"/>
+    <col min="50" max="16384" width="11.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
@@ -815,7 +2154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
@@ -823,103 +2162,135 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11"/>
     </row>
-    <row r="5" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+    </row>
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" s="2">
+        <v>0.1019</v>
+      </c>
       <c r="D12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="2">
+        <f>B12/B13*1000*1000</f>
+        <v>1018.9999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="2">
+        <v>100</v>
+      </c>
+      <c r="E13" s="3">
+        <f>$E$12/10</f>
+        <v>101.89999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="B16" s="24"/>
+      <c r="C16" s="2">
+        <v>0.1028</v>
+      </c>
+    </row>
+    <row r="17" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="24"/>
+      <c r="C17" s="2">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="16"/>
       <c r="B18" s="16"/>
     </row>
-    <row r="19" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
+    <row r="19" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="27"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
+      <c r="B19" s="24"/>
+      <c r="C19" s="2">
+        <v>0.25040000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="24"/>
+      <c r="C20" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="22" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:49" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="K22" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N22" s="1">
+        <f>141.019-50.1985</f>
+        <v>90.82050000000001</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:49" ht="30" x14ac:dyDescent="0.15">
       <c r="A23" s="12" t="s">
         <v>15</v>
       </c>
@@ -938,54 +2309,183 @@
       <c r="F23" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="15"/>
-    </row>
-    <row r="24" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
+      <c r="G23" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" s="1" cm="1">
+        <f t="array" ref="H23:I27">LINEST(E24:E28,D24:D28,1,1)</f>
+        <v>96894.278244602523</v>
+      </c>
+      <c r="I23" s="1">
+        <v>22469.320312500466</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="3">
+        <f>$E$12/10</f>
+        <v>101.89999999999999</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3">
+        <v>50</v>
+      </c>
+      <c r="D24" s="3">
+        <f>$E$13*B24/C24</f>
+        <v>2.0379999999999998</v>
+      </c>
+      <c r="E24" s="3">
+        <v>208195</v>
+      </c>
       <c r="F24" s="3"/>
       <c r="G24" s="14"/>
-    </row>
-    <row r="25" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
+      <c r="H24" s="1">
+        <v>673.06483097418015</v>
+      </c>
+      <c r="I24" s="1">
+        <v>7686.4516922205912</v>
+      </c>
+      <c r="K24" s="1">
+        <v>938329</v>
+      </c>
+      <c r="L24" s="1">
+        <f>(K24-I23)/H23</f>
+        <v>9.4521544128279551</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N24" s="1">
+        <f>L25*100*N22/10*1000</f>
+        <v>85.844938985024129</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="3">
+        <f t="shared" ref="A25:A28" si="0">$E$12/10</f>
+        <v>101.89999999999999</v>
+      </c>
+      <c r="B25" s="3">
+        <v>2</v>
+      </c>
+      <c r="C25" s="3">
+        <v>50</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" ref="D25:D28" si="1">$E$13*B25/C25</f>
+        <v>4.0759999999999996</v>
+      </c>
+      <c r="E25" s="3">
+        <v>424659</v>
+      </c>
       <c r="F25" s="3"/>
       <c r="G25" s="14"/>
-    </row>
-    <row r="26" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="H25" s="1">
+        <v>0.9998552642136983</v>
+      </c>
+      <c r="I25" s="1">
+        <v>9815.1300538483429</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L25" s="1">
+        <f>L24/1000000*10</f>
+        <v>9.4521544128279542E-5</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="3">
+        <f t="shared" si="0"/>
+        <v>101.89999999999999</v>
+      </c>
+      <c r="B26" s="3">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3">
+        <v>50</v>
+      </c>
+      <c r="D26" s="3">
+        <f t="shared" si="1"/>
+        <v>8.1519999999999992</v>
+      </c>
+      <c r="E26" s="3">
+        <v>821661</v>
+      </c>
       <c r="F26" s="3"/>
       <c r="G26" s="14"/>
-    </row>
-    <row r="27" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
+      <c r="H26" s="1">
+        <v>20724.423926432388</v>
+      </c>
+      <c r="I26" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="3">
+        <f t="shared" si="0"/>
+        <v>101.89999999999999</v>
+      </c>
+      <c r="B27" s="3">
+        <v>6</v>
+      </c>
+      <c r="C27" s="3">
+        <v>50</v>
+      </c>
+      <c r="D27" s="3">
+        <f t="shared" si="1"/>
+        <v>12.228</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1205257</v>
+      </c>
       <c r="F27" s="3"/>
       <c r="G27" s="14"/>
-    </row>
-    <row r="28" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
+      <c r="H27" s="1">
+        <v>1996524226438.8782</v>
+      </c>
+      <c r="I27" s="1">
+        <v>289010333.92187089</v>
+      </c>
+    </row>
+    <row r="28" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="3">
+        <f t="shared" si="0"/>
+        <v>101.89999999999999</v>
+      </c>
+      <c r="B28" s="3">
+        <v>10</v>
+      </c>
+      <c r="C28" s="3">
+        <v>50</v>
+      </c>
+      <c r="D28" s="3">
+        <f t="shared" si="1"/>
+        <v>20.38</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1994397</v>
+      </c>
       <c r="F28" s="3"/>
       <c r="G28" s="14"/>
     </row>
-    <row r="29" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -994,7 +2494,7 @@
       <c r="F29" s="3"/>
       <c r="G29" s="14"/>
     </row>
-    <row r="30" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -1003,8 +2503,8 @@
       <c r="F30" s="2"/>
       <c r="G30" s="14"/>
     </row>
-    <row r="31" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="7" t="s">
         <v>20</v>
       </c>
@@ -1070,91 +2570,91 @@
       <c r="AV32" s="5"/>
       <c r="AW32" s="6"/>
     </row>
-    <row r="33" spans="1:49" ht="300" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="22"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-      <c r="K33" s="21"/>
-      <c r="L33" s="21"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="20"/>
-      <c r="O33" s="21"/>
-      <c r="P33" s="21"/>
-      <c r="Q33" s="21"/>
-      <c r="R33" s="21"/>
-      <c r="S33" s="22"/>
-      <c r="T33" s="20"/>
-      <c r="U33" s="21"/>
-      <c r="V33" s="21"/>
-      <c r="W33" s="21"/>
-      <c r="X33" s="21"/>
-      <c r="Y33" s="22"/>
-      <c r="Z33" s="20"/>
-      <c r="AA33" s="21"/>
-      <c r="AB33" s="21"/>
-      <c r="AC33" s="21"/>
-      <c r="AD33" s="21"/>
-      <c r="AE33" s="22"/>
-      <c r="AF33" s="20"/>
-      <c r="AG33" s="21"/>
-      <c r="AH33" s="21"/>
-      <c r="AI33" s="21"/>
-      <c r="AJ33" s="21"/>
-      <c r="AK33" s="22"/>
-      <c r="AL33" s="20"/>
-      <c r="AM33" s="21"/>
-      <c r="AN33" s="21"/>
-      <c r="AO33" s="21"/>
-      <c r="AP33" s="21"/>
-      <c r="AQ33" s="22"/>
-      <c r="AR33" s="20"/>
-      <c r="AS33" s="21"/>
-      <c r="AT33" s="21"/>
-      <c r="AU33" s="21"/>
-      <c r="AV33" s="21"/>
-      <c r="AW33" s="22"/>
-    </row>
-    <row r="34" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:49" ht="300" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="18"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="20"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="19"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="19"/>
+      <c r="V33" s="19"/>
+      <c r="W33" s="19"/>
+      <c r="X33" s="19"/>
+      <c r="Y33" s="20"/>
+      <c r="Z33" s="18"/>
+      <c r="AA33" s="19"/>
+      <c r="AB33" s="19"/>
+      <c r="AC33" s="19"/>
+      <c r="AD33" s="19"/>
+      <c r="AE33" s="20"/>
+      <c r="AF33" s="18"/>
+      <c r="AG33" s="19"/>
+      <c r="AH33" s="19"/>
+      <c r="AI33" s="19"/>
+      <c r="AJ33" s="19"/>
+      <c r="AK33" s="20"/>
+      <c r="AL33" s="18"/>
+      <c r="AM33" s="19"/>
+      <c r="AN33" s="19"/>
+      <c r="AO33" s="19"/>
+      <c r="AP33" s="19"/>
+      <c r="AQ33" s="20"/>
+      <c r="AR33" s="18"/>
+      <c r="AS33" s="19"/>
+      <c r="AT33" s="19"/>
+      <c r="AU33" s="19"/>
+      <c r="AV33" s="19"/>
+      <c r="AW33" s="20"/>
+    </row>
+    <row r="34" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
       <c r="D34" s="3"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-    </row>
-    <row r="35" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+    </row>
+    <row r="35" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
       <c r="D35" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-    </row>
-    <row r="36" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="28" t="s">
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+    </row>
+    <row r="36" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="28" t="s">
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-    </row>
-    <row r="37" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+    </row>
+    <row r="37" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="14"/>
       <c r="B37" s="15"/>
       <c r="C37" s="15"/>
@@ -1162,7 +2662,7 @@
       <c r="E37" s="15"/>
       <c r="F37" s="15"/>
     </row>
-    <row r="38" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="8" t="s">
         <v>31</v>
       </c>
@@ -1170,28 +2670,30 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:49" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="18"/>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-      <c r="L39" s="18"/>
-      <c r="M39" s="18"/>
-      <c r="N39" s="18"/>
-      <c r="O39" s="18"/>
-      <c r="P39" s="18"/>
-      <c r="Q39" s="18"/>
-      <c r="R39" s="18"/>
-      <c r="S39" s="19"/>
-    </row>
-    <row r="40" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:49" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
+      <c r="H39" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="26"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="26"/>
+      <c r="S39" s="27"/>
+    </row>
+    <row r="40" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
         <v>33</v>
       </c>
@@ -1208,7 +2710,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
         <v>37</v>
       </c>
@@ -1217,7 +2719,7 @@
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
     </row>
-    <row r="43" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
         <v>38</v>
       </c>
@@ -1226,13 +2728,13 @@
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
     </row>
-    <row r="44" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="45" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="2" t="s">
         <v>40</v>
       </c>
@@ -1240,22 +2742,22 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
     </row>
-    <row r="48" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
     </row>
-    <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="7" t="s">
         <v>41</v>
       </c>
@@ -1266,21 +2768,21 @@
       <c r="F50" s="6"/>
       <c r="G50" s="14"/>
     </row>
-    <row r="51" spans="1:13" ht="200.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="20"/>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="22"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="23"/>
-      <c r="J51" s="23"/>
-      <c r="K51" s="23"/>
-      <c r="L51" s="23"/>
-      <c r="M51" s="23"/>
-    </row>
-    <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="200" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="18"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="20"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+    </row>
+    <row r="52" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="8"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -1289,7 +2791,7 @@
       <c r="F52" s="14"/>
       <c r="G52" s="14"/>
     </row>
-    <row r="53" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="8" t="s">
         <v>42</v>
       </c>
@@ -1300,15 +2802,15 @@
       <c r="F53" s="14"/>
       <c r="G53" s="14"/>
     </row>
-    <row r="54" spans="1:13" ht="300" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="24"/>
-      <c r="B54" s="24"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-    </row>
-    <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="300" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A54" s="21"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+    </row>
+    <row r="55" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="14"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -1317,7 +2819,7 @@
       <c r="F55" s="14"/>
       <c r="G55" s="14"/>
     </row>
-    <row r="56" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="14"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -1326,7 +2828,7 @@
       <c r="F56" s="14"/>
       <c r="G56" s="14"/>
     </row>
-    <row r="57" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="14"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -1335,7 +2837,7 @@
       <c r="F57" s="14"/>
       <c r="G57" s="14"/>
     </row>
-    <row r="58" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="14"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -1346,21 +2848,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="AL33:AQ33"/>
-    <mergeCell ref="AR33:AW33"/>
-    <mergeCell ref="N33:S33"/>
-    <mergeCell ref="T33:Y33"/>
-    <mergeCell ref="Z33:AE33"/>
-    <mergeCell ref="AF33:AK33"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
     <mergeCell ref="H39:S39"/>
     <mergeCell ref="A51:F51"/>
     <mergeCell ref="H51:M51"/>
@@ -1371,9 +2858,25 @@
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="E36:F36"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="AL33:AQ33"/>
+    <mergeCell ref="AR33:AW33"/>
+    <mergeCell ref="N33:S33"/>
+    <mergeCell ref="T33:Y33"/>
+    <mergeCell ref="Z33:AE33"/>
+    <mergeCell ref="AF33:AK33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1381,7 +2884,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
